--- a/business_forms/038_weekly_retail_performance_report--business_forms.xlsx
+++ b/business_forms/038_weekly_retail_performance_report--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'4-1',_'name':_'transactions',_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '4-1', 'name': 'transactions', 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'4-1-1',_'name':_'transactions_1',_'label':_'0-10'}</t>
+          <t>0-10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '4-1-1', 'name': 'transactions_1', 'label': '0-10'}</t>
+          <t>0-10</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'4-1-2',_'name':_'transactions_1_1',_'label':_'11-20'}</t>
+          <t>11-20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '4-1-2', 'name': 'transactions_1_1', 'label': '11-20'}</t>
+          <t>11-20</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'4-1-3',_'name':_'transactions_20_30',_'label':_'21-30'}</t>
+          <t>21-30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '4-1-3', 'name': 'transactions_20_30', 'label': '21-30'}</t>
+          <t>21-30</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'6-1',_'name':_'inventory_status',_'label':_'in_stock'}</t>
+          <t>in_stock</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '6-1', 'name': 'inventory_status', 'label': 'In Stock'}</t>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'6-1-1',_'name':_'inventory_status_1',_'label':_'out_of_stock'}</t>
+          <t>out_of_stock</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '6-1-1', 'name': 'inventory_status_1', 'label': 'Out of Stock'}</t>
+          <t>Out of Stock</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'6-1-2',_'name':_'inventory_status_1_1',_'label':_'backorder'}</t>
+          <t>backorder</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '6-1-2', 'name': 'inventory_status_1_1', 'label': 'Backorder'}</t>
+          <t>Backorder</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'6-1-3',_'name':_'inventory_status_1_1_1',_'label':_'discontinued'}</t>
+          <t>discontinued</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '6-1-3', 'name': 'inventory_status_1_1_1', 'label': 'Discontinued'}</t>
+          <t>Discontinued</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'25-1',_'name':_'submitted_by',_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '25-1', 'name': 'submitted_by', 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'25-1-1',_'name':_'submitted_by_1',_'label':_'assistant_manager'}</t>
+          <t>assistant_manager</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '25-1-1', 'name': 'submitted_by_1', 'label': 'Assistant Manager'}</t>
+          <t>Assistant Manager</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'25-1-2',_'name':_'submitted_by_1_1',_'label':_'store_owner'}</t>
+          <t>store_owner</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': '25-1-2', 'name': 'submitted_by_1_1', 'label': 'Store Owner'}</t>
+          <t>Store Owner</t>
         </is>
       </c>
     </row>
